--- a/data/processed/cdf.xlsx
+++ b/data/processed/cdf.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yipho/anes/cumulative_anes/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5943E686-0FF0-A34C-AA82-FC5CDDA9D98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4031B544-88F7-3E47-9BBE-07DCD6A14993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="14160" windowHeight="15400" xr2:uid="{3E9128F5-EFF8-A641-AEC4-52663B1E9FB6}"/>
-    <workbookView xWindow="14460" yWindow="660" windowWidth="14180" windowHeight="15400" activeTab="1" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
+    <workbookView xWindow="14500" yWindow="660" windowWidth="14160" windowHeight="15420" activeTab="1" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
   </bookViews>
   <sheets>
     <sheet name="cdf" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,7 +40,7 @@
     <author>tc={AB143EFC-31F3-3C45-9383-00A5B85114D7}</author>
   </authors>
   <commentList>
-    <comment ref="B23" authorId="0" shapeId="0" xr:uid="{92CB0C68-B0E4-E84C-8E72-4F12B3D70530}">
+    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{92CB0C68-B0E4-E84C-8E72-4F12B3D70530}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -36,7 +48,7 @@
     2016: Instead of saying near future, 2016 says "next twelve months"</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="1" shapeId="0" xr:uid="{AB143EFC-31F3-3C45-9383-00A5B85114D7}">
+    <comment ref="B28" authorId="1" shapeId="0" xr:uid="{AB143EFC-31F3-3C45-9383-00A5B85114D7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -49,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="891">
   <si>
     <t>Variable</t>
   </si>
@@ -3880,33 +3892,6 @@
     <t xml:space="preserve">We are interested in how people are getting along financially thesedays. Would you say that [you / you and your family living here] are much better off financially, somewhat better off, about the same, somewhat worse off, or much worse off than you were a year ago? </t>
   </si>
   <si>
-    <t>PRE: HAS R DONE ANY OF THE FOLLOWING - DIPPED INTO SAVINGS</t>
-  </si>
-  <si>
-    <t>2024: V241568d
-1992: V923436
-1984: V840161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2024)   
-0. Not mentioned
-1. Mentioned 
-(1992/1984)  
-1.  YES                                                     
-5.  NO  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2024)
--9. Refused
--5. Break oﬀ, suﬃcient partial
--1. Inapplicable
-(1992/1984)
-8. DK 
-9. NA
-0. Inap
-</t>
-  </si>
-  <si>
     <t>POST: CSES: STATE OF ECONOMY BETTER OR WORSE OVER PAST 12 MONTHS</t>
   </si>
   <si>
@@ -3916,11 +3901,6 @@
   <si>
     <t>Now for questions on different topics. Do the health benefits of vaccinations generally outweigh the risks, do the risks outweigh the benefits, or is there no difference?
 Are the [health benefits/risks] of vaccinations much greater, moderately greater, or slightly greater?</t>
-  </si>
-  <si>
-    <t>In the past year, have you done any of the following? Mark all that
-apply. (2024)
-IN THE PAST YEAR HAVE YOU (AND YOUR FAMILY) HAD TO USE YOUR SAVINGS TO MAKE ENDS MEET? (1984/1992)</t>
   </si>
   <si>
     <t>When it comes to people trying to improve their financial well- being, do you think it is now easier, harder, or the same as it was 20 years ago?
@@ -3958,6 +3938,89 @@
 5. Oppose a little
 6. Oppose a moderate
 7. Oppose a great deal</t>
+  </si>
+  <si>
+    <t>2024: V241262
+2020: V201301
+2008: V083141a</t>
+  </si>
+  <si>
+    <t>2024: V241265
+2020: V201304
+2008: V083142a</t>
+  </si>
+  <si>
+    <t>2024: V241271
+2020: V201310
+2008: V083144a</t>
+  </si>
+  <si>
+    <t>2024: V241274
+2020: V201313
+2008: V083145a</t>
+  </si>
+  <si>
+    <t>2024: V241268
+2020: V201307
+2008: V083149a</t>
+  </si>
+  <si>
+    <t>2024: V241277
+2020: V201316
+2008: V083140a</t>
+  </si>
+  <si>
+    <t>2024: V241283
+2020: V201322
+2008: V083151a</t>
+  </si>
+  <si>
+    <t>2024: V241280
+2020: V201319
+2008: V083148a</t>
+  </si>
+  <si>
+    <t>(2020/2024)
+1. A lot
+2. A little
+(2008)
+1. A great deal
+2. A moderate amount
+3. A little</t>
+  </si>
+  <si>
+    <t>2024: V241336
+2020: V201379
+2016: V161171</t>
+  </si>
+  <si>
+    <t>POST: CSES: AGREE/DISAGREE: R UNDERSTANDS MOST IMPORTANT POLITICAL ISSUES</t>
+  </si>
+  <si>
+    <t>(2016/2020)
+1. Never
+2. Once in a while
+3. About half the time
+4. Most of the time
+5. All the time
+(2024)
+1. Yes
+2. No</t>
+  </si>
+  <si>
+    <t>How much do you feel it is justified for people to use violence to pursue their political goals in this country?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2020/2024)
+-9. Refused
+-8. Don’t know
+-1. Inapplicable
+(1968)
+8.  DK                                                   
+9.  NA; NO POST-ELECTION INTERVIEW </t>
+  </si>
+  <si>
+    <t xml:space="preserve">How much do you care who wins the presidential election this fall? </t>
   </si>
 </sst>
 </file>
@@ -4448,7 +4511,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4456,6 +4519,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4837,10 +4907,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B23" dT="2025-11-13T20:41:49.60" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{92CB0C68-B0E4-E84C-8E72-4F12B3D70530}">
+  <threadedComment ref="B22" dT="2025-11-13T20:41:49.60" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{92CB0C68-B0E4-E84C-8E72-4F12B3D70530}">
     <text>2016: Instead of saying near future, 2016 says "next twelve months"</text>
   </threadedComment>
-  <threadedComment ref="B29" dT="2025-11-13T22:43:53.76" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{AB143EFC-31F3-3C45-9383-00A5B85114D7}">
+  <threadedComment ref="B28" dT="2025-11-13T22:43:53.76" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{AB143EFC-31F3-3C45-9383-00A5B85114D7}">
     <text>All years regard the "transgender policy" to the policy of transgender people using bathrooms related to their gender identity. Does the question summary require the whole concept? or can we just say "Transgender policy"?</text>
   </threadedComment>
 </ThreadedComments>
@@ -6387,7 +6457,7 @@
         <v>71</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>313</v>
@@ -8927,14 +8997,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F06C183-D354-5B46-AC5B-69BA44B64C6F}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" customWidth="1"/>
     <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -8959,7 +9029,7 @@
     </row>
     <row r="2" spans="1:6" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
@@ -8978,8 +9048,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>31</v>
+      <c r="A3" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>32</v>
@@ -8998,8 +9068,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>38</v>
+      <c r="A4" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>39</v>
@@ -9018,8 +9088,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>45</v>
+      <c r="A5" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>46</v>
@@ -9039,7 +9109,7 @@
     </row>
     <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>53</v>
@@ -9059,13 +9129,13 @@
     </row>
     <row r="7" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>71</v>
@@ -9079,13 +9149,13 @@
     </row>
     <row r="8" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>87</v>
@@ -9099,7 +9169,7 @@
     </row>
     <row r="9" spans="1:6" ht="323" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>91</v>
@@ -9119,7 +9189,7 @@
     </row>
     <row r="10" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>862</v>
@@ -9139,7 +9209,7 @@
     </row>
     <row r="11" spans="1:6" ht="289" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>117</v>
@@ -9159,7 +9229,7 @@
     </row>
     <row r="12" spans="1:6" ht="174" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>130</v>
@@ -9179,7 +9249,7 @@
     </row>
     <row r="13" spans="1:6" ht="202" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>138</v>
@@ -9199,7 +9269,7 @@
     </row>
     <row r="14" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>150</v>
@@ -9217,235 +9287,235 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>866</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>873</v>
+        <v>168</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>868</v>
+        <v>169</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>869</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>867</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="227" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>870</v>
+        <v>174</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>178</v>
+        <v>869</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="223" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>874</v>
+        <v>198</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="306" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="306" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
+        <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>260</v>
+        <v>227</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>871</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>60</v>
+        <v>281</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>876</v>
+        <v>291</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>281</v>
@@ -9454,421 +9524,762 @@
         <v>282</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>281</v>
+        <v>872</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>282</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>299</v>
+        <v>873</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>877</v>
+        <v>71</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="289" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>878</v>
+        <v>322</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="289" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="272" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="272" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>313</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>879</v>
+        <v>354</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>71</v>
+        <v>356</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>356</v>
+        <v>884</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>368</v>
+        <v>884</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F35" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F36" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F37" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F43" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>450</v>
+      </c>
       <c r="F44" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="F45" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="221" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>889</v>
+      </c>
       <c r="F46" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F47" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="F48" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="49" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="F49" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="50" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="F50" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="51" spans="6:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="F51" s="1" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="52" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>515</v>
+      </c>
       <c r="F52" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="53" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>522</v>
+      </c>
       <c r="F53" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="54" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="F54" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="55" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>546</v>
+      </c>
       <c r="F55" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="56" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>553</v>
+      </c>
       <c r="F56" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="57" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>561</v>
+      </c>
       <c r="F57" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="58" spans="6:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="F58" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F59" t="s">
+    <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F58" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="60" spans="6:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>591</v>
+      </c>
       <c r="F60" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="61" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>604</v>
+      </c>
       <c r="F61" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="62" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>617</v>
+      </c>
       <c r="F62" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="63" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>628</v>
+      </c>
       <c r="F63" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="64" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>637</v>
+      </c>
       <c r="F64" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="65" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>648</v>
+      </c>
       <c r="F65" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="66" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>658</v>
+      </c>
       <c r="F66" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="67" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>668</v>
+      </c>
       <c r="F67" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="68" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>677</v>
+      </c>
       <c r="F68" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="69" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>684</v>
+      </c>
       <c r="F69" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="70" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>694</v>
+      </c>
       <c r="F70" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="71" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>708</v>
+      </c>
       <c r="F71" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="72" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>719</v>
+      </c>
       <c r="F72" s="1" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="73" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>731</v>
+      </c>
       <c r="F73" s="1" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="74" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>741</v>
+      </c>
       <c r="F74" s="1" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="75" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>751</v>
+      </c>
       <c r="F75" s="1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="76" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>762</v>
+      </c>
       <c r="F76" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="77" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>773</v>
+      </c>
       <c r="F77" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>781</v>
+      </c>
       <c r="F78" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="79" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>793</v>
+      </c>
       <c r="F79" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="80" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>802</v>
+      </c>
       <c r="F80" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="81" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>811</v>
+      </c>
       <c r="F81" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="82" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>821</v>
+      </c>
       <c r="F82" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="83" spans="6:6" ht="68" x14ac:dyDescent="0.2">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>831</v>
+      </c>
       <c r="F83" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="84" spans="6:6" ht="51" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>840</v>
+      </c>
       <c r="F84" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="85" spans="6:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="F85" s="1" t="s">
         <v>856</v>
       </c>
     </row>

--- a/data/processed/cdf.xlsx
+++ b/data/processed/cdf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yipho/anes/cumulative_anes/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4031B544-88F7-3E47-9BBE-07DCD6A14993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEFACD6-12C0-D64C-A29F-C380C0E146C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14500" yWindow="660" windowWidth="14160" windowHeight="15420" activeTab="1" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
+    <workbookView xWindow="14480" yWindow="660" windowWidth="14160" windowHeight="15400" activeTab="1" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
   </bookViews>
   <sheets>
     <sheet name="cdf" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,8 @@
   <authors>
     <author>tc={92CB0C68-B0E4-E84C-8E72-4F12B3D70530}</author>
     <author>tc={AB143EFC-31F3-3C45-9383-00A5B85114D7}</author>
+    <author>tc={DFD8C8CE-6327-EB4D-BAE5-C4F37EA7D163}</author>
+    <author>tc={A687251A-029A-8848-BF21-9CE631347539}</author>
   </authors>
   <commentList>
     <comment ref="B22" authorId="0" shapeId="0" xr:uid="{92CB0C68-B0E4-E84C-8E72-4F12B3D70530}">
@@ -56,12 +58,28 @@
     All years regard the "transgender policy" to the policy of transgender people using bathrooms related to their gender identity. Does the question summary require the whole concept? or can we just say "Transgender policy"?</t>
       </text>
     </comment>
+    <comment ref="A51" authorId="2" shapeId="0" xr:uid="{DFD8C8CE-6327-EB4D-BAE5-C4F37EA7D163}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    For 2024, it just mentions "congress and president" but in the other years 2020/2016, it specifies US senate or House of Reps. </t>
+      </text>
+    </comment>
+    <comment ref="A71" authorId="3" shapeId="0" xr:uid="{A687251A-029A-8848-BF21-9CE631347539}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    in 2016, this is a pre and post question.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="908">
   <si>
     <t>Variable</t>
   </si>
@@ -4022,12 +4040,259 @@
   <si>
     <t xml:space="preserve">How much do you care who wins the presidential election this fall? </t>
   </si>
+  <si>
+    <t>POST: CSES: HOW INTERESTED IN POLITICS IS R</t>
+  </si>
+  <si>
+    <t>POST: CSES: HOW CLOSELY DOES R FOLLOW POLITICS IN MEDIA</t>
+  </si>
+  <si>
+    <t>How much does Congress pass laws to benefit organizations that spend money to support candidates</t>
+  </si>
+  <si>
+    <t>0. Not mentioned
+1. Mentioned</t>
+  </si>
+  <si>
+    <t>-9. Refused
+-1. Inapplicable
+-8. Don’t know (FTF only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How easy was it for you to get access to a computer with an internet connection to take this survey? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9. Refused
+-7. No post-election data, deleted due to incomplete interview
+-6. No post-election interview
+-5. Interview breakoff (sufficient partial IW)
+-4. Technical error
+-1. Inapplicable
+</t>
+  </si>
+  <si>
+    <t>-9. Refused
+-7. No post-election data, deleted due to incomplete interview
+-6. No post-election interview
+-5. Interview breakoff (sufficient partial IW)
+-4. Technical error
+-1. Inapplicable</t>
+  </si>
+  <si>
+    <t>(2024) 
+How important is it for immigrants to adapt to the customs and traditions of the United States?
+(2020/2016)
+Now thinking about minorities in the United States. Do you agree strongly, agree somewhat, neither agree nor disagree, disagree somewhat, or disagree strongly with the following statement? ‘Minorities should adapt to the customs and traditions of the United States.’</t>
+  </si>
+  <si>
+    <t>(2024)
+1. Not at all important
+2. A little important
+3. Moderately important
+4. Very important
+5. Extremely important
+(2020/2016) 
+1. Agree strongly
+2. Agree somewhat
+3. Neither agree nor disagree
+4. Disagree somewhat
+5. Disagree strongly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2024)
+Are immigrants generally good or bad for America’s economy? 
+(2020/2016)
+And now thinking specifically about immigrants. Do you agree strongly, agree somewhat, neither agree nor disagree, disagree somewhat, or disagree strongly with the following statement? ‘Immigrants are generally good for America’s economy.’
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2024)
+1. Extremely good
+2. Moderately good
+3. Slightly good
+4. Neither good nor bad
+5. Slightly bad
+6. Moderately bad
+7. Extremely bad
+(2020/2016)
+1. Agree strongly
+2. Agree somewhat
+3. Neither agree nor disagree
+4. Disagree somewhat
+5. Disagree strongly
+</t>
+  </si>
+  <si>
+    <t>POST: CSES: OUT-GROUP ATTITUDES: IMMIGRANTS INCREASE CRIME</t>
+  </si>
+  <si>
+    <t>How much does R agree or disagree that immigrants increase crime rates in the United States?</t>
+  </si>
+  <si>
+    <t>-9. Refused
+-1. Inapplicable
+-6. No post-election interview
+-7. No post data, deleted due</t>
+  </si>
+  <si>
+    <t>010. Protestant, NFS, other, unknown, inter-, or non-denominational
+099. Christian, NFS, unknown, inter-, or non-denominational
+100. 7th Day Adventist
+101. Sabbatarian
+109. Adventist (NFS)
+110. Episcopalian; Anglican
+120. American Baptist Association
+121. American Baptist Churches USA (wrongly aka 'Northern Baptist')
+122. Baptist Bible Fellowship
+123. Baptist General Conference
+124. Missionary Baptist; Baptist Missionary Association of America
+125. Conservative Baptist Association of America
+126. General Association of Regular Baptist Churches; GARB
+127. National Association of Free Will Baptists; United Free Will Baptist
+Church
+128. Primitive Baptist
+129. National Baptist Convention in the USA
+130. National Baptist Convention of America
+131. National Primitive Baptist Convention of the USA
+132. Progressive National Baptist Convention
+133. National Baptist Convention NFS
+134. Reformed Baptist (Calvinist)
+135. Southern Baptist Convention
+136. Full Gospel Baptist Church Fellowship
+149. Baptist (NFS or other Baptist group not in codes 120-135)
+150. United Church of Christ; UCC; Congregational; Congregationalist;
+Evangelical and Reformed Church
+155. Congregational Christian
+160. Church of the Brethren
+161. Brethren (NFS)
+162. Mennonite Church
+163. Moravian Church
+164. Old Order Amish
+165. Quakers; Friends
+166. Evangelical Covenant Church (not Anabaptist in tradition)
+167. Evangelical Free Church, EFC, or EFCA (not Anabaptist in tradition)
+168. Brethren in Christ
+169. Apostolic Christian Church of America
+170. Mennonite Brethren
+171. Apostolic Christian Church Nazarene
+180. Christian and Missionary Alliance; CMA; Alliance
+181. Church of God (Anderson, IN)
+182. Church of the Nazarene
+183. Free Methodist Church
+184. Salvation Army
+185. Wesleyan Church
+186. Church of God of Findlay, OH
+199. Pentecostal (NFS); Church of God (NFS); Holiness (NFS); not ascertained
+whether R Pentecostal or Charismatic (Holin
+200. Plymouth Brethren
+201. Independent Fundamental Churches of America; IFCA
+219. Independent-Fundamentalist (NFS)
+220. Evangelical Lutheran Church in America (formerly Lutheran Church in
+America and The American Lutheran Church); ELCA
+221. Lutheran Church, Missouri Synod; LC-MS
+222. Wisconsin Evangelical Lutheran Synod; WELS
+224. Lutheran Free Church, Association of Free Lutheran Churches, AFLC
+225. Church of the Lutheran Brethren
+229. Lutheran (other or NFS)
+230. United Methodist Church; Evangelical United Brethren
+231. African Methodist Episcopal Church; AME
+232. African Methodist Episcopal Zion Church
+233. Christian Methodist Episcopal Church
+234. Primitive Methodist
+235. Congregational Methodist (fundamentalist)
+240. Fire-Baptized Holiness
+242. Assemblies of the Lord Jesus Christ; AJLC
+243. Church of Our Lord Jesus Christ of the Apostolic Faith; COOLJC
+244. Church of the Lord Jesus Christ of the Apostolic Faith; CLJC
+245. Bible Way Church of Our Lord Jesus Christ
+246. International Bible Way Church of Our Lord Jesus Christ
+249. Methodist (other or NFS)
+250. Assemblies of God; Assembly of God
+251. Church of God (Cleveland, TN)
+252. Church of God (Huntsville, AL)
+253. International Church of the Four Square Gospel
+254. Pentecostal Church of God
+255. Pentecostal Holiness Church
+256. United Pentecostal Church International
+257. Church of God in Christ (incl. not ascertained whether 258)
+258. Church of God in Christ International
+260. Church of God of the Apostolic Faith
+261. Church of God of Prophecy
+262. Vineyard Fellowship
+263. Open Bible Standard Churches
+264. Full Gospel
+267. Apostolic Pentecostal
+270. Presbyterian Church in the U.S.A.
+271. Cumberland Presbyterian Church
+272. Presbyterian Church in America; PCA
+275. Evangelical Presbyterian
+276. Reformed Presbyterian
+279. Presbyterian (other or NFS)
+280. Christian Reformed Church (inaccurately known as 'Dutch Reformed')
+281. Reformed Church in America
+289. Reformed (other or NFS)
+290. Christian Church; Disciples of Christ
+291. Christian Churches and Churches of Christ
+292. Churches of Christ; Church of Christ (NFS)
+293. Christian Congregation
+300. Christian Scientists
+301. Mormons; Latter Day Saints; Community of Christ
+303. Unitarian; Universalist
+304. Jehovah's Witnesses
+305. Unity; Unity Church; Christ Church Unity
+306. Fundamentalist Adventist; Worldwide Church of God; United Church of God
+400. Roman Catholic
+501. Orthodox
+502. Conservative
+503. Reform
+524. Jewish, other, no preference, or NFS
+600. Catholic and  Protestant
+650. Messianic Judaism; Jews for Jesus
+695. More than 1 major religion (e.g., Christian, Jewish, Muslim, etc.)
+700. Greek Rite Catholic
+701. Greek Orthodox
+702. Russian Orthodox
+703. Rumanian Orthodox
+704. Serbian Orthodox
+705. Syrian Orthodox
+706. Armenian Orthodox
+707. Georgian Orthodox
+708. Ukrainian Orthodox
+719. Eastern Orthodox (NFS or other specific Orthodox church)
+720. Muslim; Islam
+721. Buddhist
+722. Hindu
+723. Baha'i; Bahai
+724. American Indian religions; Native American religions
+725. New Age
+726. Wicca; Wiccan
+727. Pagan
+730. Sikh
+732. Konko Church
+735. Spiritualists (not 'spiritual; must refer specifically to
+'Spiritualism' or 'Spiritualists')
+736. Religious Science; Science of Mind (not Scientology; not Christian
+Scientists); Centers for Spiritual Living
+740. Other non-Christian /non-Jewish
+750. Scientology
+790. Religious /ethical cults
+870. Other tradition not codeable to 010-790
+879. R indicates having an affiliation but does not specify one
+880. None
+888. DK whether considers self as part of a particular religion
+889. RF to say if considers self as part of a particular religion</t>
+  </si>
+  <si>
+    <t>2024: V242338
+2020: V202353
+2016: V161307a; V162133</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4168,6 +4433,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -4511,7 +4782,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4525,7 +4796,12 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4913,6 +5189,12 @@
   <threadedComment ref="B28" dT="2025-11-13T22:43:53.76" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{AB143EFC-31F3-3C45-9383-00A5B85114D7}">
     <text>All years regard the "transgender policy" to the policy of transgender people using bathrooms related to their gender identity. Does the question summary require the whole concept? or can we just say "Transgender policy"?</text>
   </threadedComment>
+  <threadedComment ref="A51" dT="2025-11-19T20:35:46.74" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{DFD8C8CE-6327-EB4D-BAE5-C4F37EA7D163}">
+    <text xml:space="preserve">For 2024, it just mentions "congress and president" but in the other years 2020/2016, it specifies US senate or House of Reps. </text>
+  </threadedComment>
+  <threadedComment ref="A71" dT="2025-11-19T22:17:01.88" personId="{9254EDE6-B7E7-F040-A3D9-36F90150B96F}" id="{A687251A-029A-8848-BF21-9CE631347539}">
+    <text>in 2016, this is a pre and post question.</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -9000,11 +9282,11 @@
   <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="79.6640625" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" customWidth="1"/>
     <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -9023,7 +9305,7 @@
       <c r="E1" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -9407,7 +9689,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>232</v>
       </c>
@@ -9527,7 +9809,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>294</v>
       </c>
@@ -9887,7 +10169,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>453</v>
       </c>
@@ -9907,7 +10189,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="221" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>463</v>
       </c>
@@ -9927,7 +10209,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>471</v>
       </c>
@@ -10007,176 +10289,421 @@
         <v>504</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
+      <c r="B51" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>513</v>
+      </c>
       <c r="F51" s="4" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>515</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>522</v>
       </c>
+      <c r="B53" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F53" s="1" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>534</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>546</v>
       </c>
+      <c r="B55" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F55" s="1" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>553</v>
       </c>
+      <c r="B56" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F56" s="1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>561</v>
       </c>
+      <c r="B57" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F57" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="197" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F58" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>576</v>
       </c>
+      <c r="B59" t="s">
+        <v>592</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>895</v>
+      </c>
       <c r="F59" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>591</v>
       </c>
+      <c r="B60" t="s">
+        <v>606</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="F60" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>604</v>
       </c>
+      <c r="B61" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>898</v>
+      </c>
       <c r="F61" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="187" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>617</v>
       </c>
+      <c r="B62" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>897</v>
+      </c>
       <c r="F62" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>628</v>
       </c>
+      <c r="B63" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F63" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="340" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>637</v>
       </c>
+      <c r="B64" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F64" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>648</v>
       </c>
+      <c r="B65" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F65" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>658</v>
       </c>
+      <c r="B66" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F66" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>668</v>
       </c>
+      <c r="B67" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="F67" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>677</v>
       </c>
+      <c r="B68" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="F68" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>684</v>
       </c>
+      <c r="B69" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>905</v>
+      </c>
       <c r="F69" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="312" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>694</v>
       </c>
+      <c r="B70" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>716</v>
+      </c>
       <c r="F70" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
         <v>708</v>
       </c>
+      <c r="B71" t="s">
+        <v>720</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="F71" s="1" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -10184,103 +10711,100 @@
         <v>719</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>731</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>741</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>751</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>762</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>773</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>781</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>793</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>802</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>811</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>821</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>831</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>856</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/cdf.xlsx
+++ b/data/processed/cdf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yipho/anes/cumulative_anes/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEFACD6-12C0-D64C-A29F-C380C0E146C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A051CC-6EC5-9D47-AB53-22A11652092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14480" yWindow="660" windowWidth="14160" windowHeight="15400" activeTab="1" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
+    <workbookView xWindow="14480" yWindow="660" windowWidth="14160" windowHeight="15400" xr2:uid="{4F174E8A-7303-6243-8ED4-F9DB801B02F5}"/>
   </bookViews>
   <sheets>
     <sheet name="cdf" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="898">
   <si>
     <t>Variable</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>Sources</t>
-  </si>
-  <si>
-    <t>VCF9282</t>
   </si>
   <si>
     <t>POST: DISCRIMINATION IN THE US AGAINST MEN</t>
@@ -1085,9 +1082,6 @@
   </si>
   <si>
     <t>When the U.S. federal government spends more money than it collects, the difference is called the federal budget deficit. The federal government currently has a deficit. How important is it to reduce the deficit?</t>
-  </si>
-  <si>
-    <t>When the U.S. federal government spends more money than it collects, the difference is called the federal budget deficit. The federal government currently has a deficit. How important is it to reduce the deficit? [Extremely important, very important, moderately important, a little important, or not at all important? / Not at all important, a little important, moderately important, very important, or extremely important?] F or W eb administration, reference to the respondent booklet was omitted. F orward/reverse response option order</t>
   </si>
   <si>
     <t>How important is it to reduce the deficit? [EXTREMELY IMPORTANT, VERY IMPORTANT, MODERATELY IMPORTANT, A LITTLE IMPORTANT, or NOT AT ALL IMPORTANT? / NOT AT ALL IMPORTANT, A LITTLE IMPORTANT, MODERATELY IMPORTANT, VERY IMPORTANT, or EX- TREMELYIMPORTANT?]</t>
@@ -1753,10 +1747,6 @@
 -9. Refused</t>
   </si>
   <si>
-    <t>2024: V241262
-2020: V201301</t>
-  </si>
-  <si>
     <t>VCF9315</t>
   </si>
   <si>
@@ -1769,10 +1759,6 @@
     <t>How much should spending on public schools be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241265
-2020: V201304</t>
-  </si>
-  <si>
     <t>VCF9316</t>
   </si>
   <si>
@@ -1785,10 +1771,6 @@
     <t>How much should spending on crime be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241271
-2020: V201310</t>
-  </si>
-  <si>
     <t>VCF9317</t>
   </si>
   <si>
@@ -1801,10 +1783,6 @@
     <t>How much should spending on welfare be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241274
-2020: V201313</t>
-  </si>
-  <si>
     <t>VCF9318</t>
   </si>
   <si>
@@ -1817,10 +1795,6 @@
     <t>How much should spending on border security be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241268
-2020: V201307</t>
-  </si>
-  <si>
     <t>VCF9319</t>
   </si>
   <si>
@@ -1833,10 +1807,6 @@
     <t>How much should spending on highways be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241277
-2020: V201316</t>
-  </si>
-  <si>
     <t>VCF9320</t>
   </si>
   <si>
@@ -1849,10 +1819,6 @@
     <t>How much should spending on the environment be increased/decreased</t>
   </si>
   <si>
-    <t>2024: V241283
-2020: V201322</t>
-  </si>
-  <si>
     <t>VCF9321</t>
   </si>
   <si>
@@ -1863,10 +1829,6 @@
   </si>
   <si>
     <t>How much should spending on aid to the poor be increased/decreased</t>
-  </si>
-  <si>
-    <t>2024: V241280
-2020: V201319</t>
   </si>
   <si>
     <t>VCF9322</t>
@@ -3383,9 +3345,6 @@
     <t>VCF9354</t>
   </si>
   <si>
-    <t>V232338does not exist in 2024 codebook</t>
-  </si>
-  <si>
     <t>POST: IS R LOWER MIDDLE CLASS, MIDDLE CLASS, UPPER MIDDLE CLASS? [EGSS]</t>
   </si>
   <si>
@@ -3412,11 +3371,6 @@
 -6. No post-election interview
 -7. No post data, deleted due
 -9. Refused</t>
-  </si>
-  <si>
-    <t>2024: V232338
-2020: V202353
-2016: V161307a; V162133</t>
   </si>
   <si>
     <t>VCF9355</t>
@@ -3755,10 +3709,6 @@
 PRE: REQUIRE EMPLOYERS TO OFFER PAID LEAVE TO PARENTS OF NEW CHILDREN (STRENGTH)</t>
   </si>
   <si>
-    <t>PRE: Require employers to offer paid leave to parents of new children
-PRE: Strength require employers to offer paid leave to parents of new children</t>
-  </si>
-  <si>
     <t>Favor/oppose paid parental leave</t>
   </si>
   <si>
@@ -3828,32 +3778,6 @@
 3. A little</t>
   </si>
   <si>
-    <t>1. A great deal
-2. A moderate amount
-3. A little
-1. Favor a great deal
-2. Favor a moderate amount
-3. Favor a little
-4. Neither favor nor oppose
-5. Oppose a little
-6. Oppose a moderate
-7. Oppose a great deal</t>
-  </si>
-  <si>
-    <t>1. A greatdeal
-2. A moderate amount
-3. A little
-1. A great deal
-2. A moderate amount
-3. A little
-1. A great deal
-2. A moderate amount
-3. A little
-1. A great deal
-2. A moderate amount
-3. A little</t>
-  </si>
-  <si>
     <t>-1. INAP ,
 -8. Don’t know (FTF only)
 -9. Refused-8. DK (-8) in V161204,
@@ -3863,18 +3787,6 @@
     <t>-1. INAP ,</t>
   </si>
   <si>
-    <t>-1. Inapplicable
--8. Don't know
--1. Inapplicable
--8. Don't know
--1. Inapplicable
--4. Error
--8. Don't know
--1. Inapplicable
--4. Error
--8. Don't know</t>
-  </si>
-  <si>
     <t>2024: V242243; V242244
 2016: V161204a; V161204b
 2012: aa_unifav; aa_uniopp</t>
@@ -3899,10 +3811,6 @@
     <t>POST: DOES R FAVOR OR OPPOSE AFFIRMATIVE ACTION IN UNIVERSITIES</t>
   </si>
   <si>
-    <t xml:space="preserve">POST: DO POLICE TREAT BLACKS OR WHITES BETTER
-POST: HOW MUCH BETTER DO POLICE TREAT BLACKS OR WHITES POST-ELECTION </t>
-  </si>
-  <si>
     <t>In general, do the police treat whites better than blacks, treat them both thesame, or treat blacks better than whites? 
 Do the police treat [whites/blacks] much better, moderately better, or a little better?</t>
   </si>
@@ -3941,21 +3849,6 @@
   <si>
     <t>Do you favor, oppose, or neither favor nor oppose building a wall on the U.S. border with Mexico?
 Do you [favor / oppose] that a great deal, a moderate amount, or a little?</t>
-  </si>
-  <si>
-    <t>1. F avor
-2. Oppose
-3. Neither favor nor oppose
-1. A great deal
-2. A moderate amount
-3. A little
-1. F avor a great deal
-2. F avor a moderate amount
-3. F avor a little
-4. Neither favor nor oppose
-5. Oppose a little
-6. Oppose a moderate
-7. Oppose a great deal</t>
   </si>
   <si>
     <t>2024: V241262
@@ -4005,11 +3898,6 @@
 1. A great deal
 2. A moderate amount
 3. A little</t>
-  </si>
-  <si>
-    <t>2024: V241336
-2020: V201379
-2016: V161171</t>
   </si>
   <si>
     <t>POST: CSES: AGREE/DISAGREE: R UNDERSTANDS MOST IMPORTANT POLITICAL ISSUES</t>
@@ -4286,6 +4174,71 @@
     <t>2024: V242338
 2020: V202353
 2016: V161307a; V162133</t>
+  </si>
+  <si>
+    <t>(2024/2020)
+1. Now serving on active duty
+2. Previously served on active duty but not now on active duty
+3. Have never served on active duty
+(2016)
+0. Have never served on
+1. Have previously served on</t>
+  </si>
+  <si>
+    <t>"-7. Insuﬃcient partial, interview deleted
+-6. No post interview
+-1. Inapplicable"</t>
+  </si>
+  <si>
+    <t>POST: DO POLICE TREAT BLACKS OR WHITES BETTER
+POST: HOW MUCH BETTER DO POLICE TREAT BLACKS OR WHITES POST-ELECTION SURVEY VARIABLES 549</t>
+  </si>
+  <si>
+    <t>Please turn to page [PRELOAD: page] of the booklet. When the U.S. federal government spends more money than it collects, the difference is called the federal budget deficit. The federal government currently has a deficit. How important is it to reduce the deficit? [Extremely important, very important, moderately important, a little important, or not at all important? / Not at all important, a little important, moderately important, very important, or extremely important?] F or W eb administration, reference to the respondent booklet was omitted. F orward/reverse response option order</t>
+  </si>
+  <si>
+    <t>Are you in the lower middle class, the middle class, or the upper middle class? POST-ELECTION SURVEY VARIABLES 483</t>
+  </si>
+  <si>
+    <t>PRE: Require employers to offer paid leave to parents of new children
+PRE: Strength require employers to offer paid leave to parents of new chil-</t>
+  </si>
+  <si>
+    <t>1. A great deal
+2. A moderate amount
+3. A little1. F avor a great deal
+2. F avor a moderate amount
+3. F avor a little
+4. Neither favor nor oppose
+5. Oppose a little
+6. Oppose a moderate
+7. Oppose a great deal</t>
+  </si>
+  <si>
+    <t>1. A greatdeal
+2. A moderate amount
+3. A little
+1. A greatdeal
+2. A moderate amount
+3. A little
+1. A greatdeal
+2. A moderate amount
+3. A little
+1. A greatdeal
+2. A moderate amount
+3. A little</t>
+  </si>
+  <si>
+    <t>-1. Inapplicable
+-8. Don't know
+-1. Inapplicable
+-8. Don't know
+-1. Inapplicable
+-4. Error
+-8. Don't know
+-1. Inapplicable
+-4. Error
+-8. Don't know</t>
   </si>
 </sst>
 </file>
@@ -4782,7 +4735,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4796,6 +4749,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5238,7 +5192,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -5271,1628 +5225,1658 @@
     </row>
     <row r="2" spans="1:19" ht="388" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2"/>
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="388" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3"/>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="388" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4"/>
+      <c r="K4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="404" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5"/>
+      <c r="K5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6"/>
+      <c r="K6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7"/>
+      <c r="K7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8"/>
+      <c r="K8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="O8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9"/>
+      <c r="K9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M9" s="1" t="s">
+      <c r="O9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="388" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10"/>
+      <c r="K10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="O10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11"/>
+      <c r="K11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12"/>
+      <c r="K12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13"/>
+      <c r="K13" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14"/>
+      <c r="K14" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="O14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="15" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" t="s">
-        <v>150</v>
+      <c r="B15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15"/>
+        <v>166</v>
+      </c>
+      <c r="J15" t="s">
+        <v>167</v>
+      </c>
       <c r="K15" s="1" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>145</v>
+        <v>168</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="J16"/>
       <c r="K16" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="J17"/>
       <c r="K17" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
+      </c>
+      <c r="J18" t="s">
+        <v>201</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>190</v>
+        <v>110</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>192</v>
+        <v>61</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>202</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="J19"/>
       <c r="K19" s="1" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>212</v>
+        <v>892</v>
+      </c>
+      <c r="J20" t="s">
+        <v>224</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>216</v>
+        <v>61</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="J21"/>
       <c r="K21" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>238</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="J22"/>
       <c r="K22" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>248</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J23"/>
       <c r="K23" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>61</v>
+        <v>259</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>62</v>
+        <v>260</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>257</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="J24"/>
       <c r="K24" s="1" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>260</v>
+        <v>59</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>262</v>
+        <v>61</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>270</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="J25"/>
       <c r="K25" s="1" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J26"/>
+      <c r="K26" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="L26" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="221" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J27"/>
+      <c r="K27" t="s">
+        <v>299</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="221" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="K28" t="s">
-        <v>301</v>
+        <v>308</v>
+      </c>
+      <c r="J28"/>
+      <c r="K28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>283</v>
+        <v>312</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>310</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="J29"/>
       <c r="K29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="P29" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>323</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="J30"/>
       <c r="K30" s="1" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>71</v>
+        <v>333</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>334</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="J31"/>
       <c r="K31" s="1" t="s">
-        <v>335</v>
+        <v>70</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>335</v>
+        <v>70</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>345</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="J32"/>
       <c r="K32" s="1" t="s">
-        <v>71</v>
+        <v>354</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>71</v>
+        <v>354</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>875</v>
+        <v>355</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>355</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="J33"/>
       <c r="K33" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>359</v>
+        <v>858</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="J34"/>
+      <c r="K34" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="L34" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="M34" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M34" s="1" t="s">
+      <c r="O34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q34" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S34" s="1" t="s">
-        <v>371</v>
+        <v>859</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J35"/>
+      <c r="K35" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="M35" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="O35" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M35" s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S35" s="1" t="s">
-        <v>376</v>
+        <v>860</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="238" x14ac:dyDescent="0.2">
@@ -6912,360 +6896,368 @@
         <v>380</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J36"/>
+      <c r="K36" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="M36" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="O36" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M36" s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S36" s="1" t="s">
-        <v>381</v>
+        <v>861</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="G37" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J37"/>
+      <c r="K37" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="M37" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="O37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q37" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S37" s="1" t="s">
-        <v>386</v>
+        <v>862</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="G38" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J38"/>
+      <c r="K38" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="O38" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P38" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S38" s="1" t="s">
-        <v>391</v>
+        <v>863</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="G39" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J39"/>
+      <c r="K39" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="M39" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M39" s="1" t="s">
+      <c r="O39" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q39" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="S39" s="1" t="s">
-        <v>396</v>
+        <v>864</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="238" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J40"/>
+      <c r="K40" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="S40" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" ht="238" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="J41"/>
+      <c r="K41" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>146</v>
+        <v>281</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>370</v>
+        <v>282</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>413</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="J42"/>
       <c r="K42" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>282</v>
+        <v>419</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>283</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>284</v>
+        <v>112</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>425</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="J43"/>
       <c r="K43" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>428</v>
+        <v>279</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>429</v>
+        <v>59</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>430</v>
@@ -7279,93 +7271,95 @@
         <v>432</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="J44"/>
+      <c r="K44" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="M44" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="255" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="J45"/>
+      <c r="K45" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="P45" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M44" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="Q45" s="1" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="255" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>453</v>
       </c>
@@ -7375,84 +7369,86 @@
       <c r="C46" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J46"/>
+      <c r="K46" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="O46" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="S46" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>467</v>
-      </c>
+      <c r="J47"/>
       <c r="K47" s="1" t="s">
         <v>468</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="S47" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S47" s="1" t="s">
+    </row>
+    <row r="48" spans="1:19" ht="238" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>472</v>
@@ -7467,169 +7463,173 @@
         <v>475</v>
       </c>
       <c r="H48" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48"/>
+      <c r="K48" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="L48" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>478</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>146</v>
+        <v>479</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>147</v>
+        <v>441</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>113</v>
+        <v>480</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="238" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="289" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>486</v>
       </c>
+      <c r="J49"/>
       <c r="K49" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="O49" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M49" s="1" t="s">
+      <c r="P49" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S49" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="O49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:19" ht="388" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q49" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="S49" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" ht="289" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="I50" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J50"/>
+      <c r="K50" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="S50" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="F50" s="1" t="s">
+    </row>
+    <row r="51" spans="1:19" ht="404" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="O50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" ht="388" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="I51" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="J51"/>
+      <c r="K51" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="L51" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="Q51" s="1" t="s">
-        <v>490</v>
+        <v>61</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>504</v>
@@ -7640,160 +7640,163 @@
         <v>505</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="G52" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="I52" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J52"/>
+      <c r="K52" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="M52" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="O52" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="Q52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S52" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="K52" s="1" t="s">
+    </row>
+    <row r="53" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="P52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="Q52" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" ht="404" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>518</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>518</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="J53"/>
       <c r="K53" s="1" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>529</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="J54"/>
       <c r="K54" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>532</v>
+        <v>26</v>
       </c>
       <c r="P54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q54" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="Q54" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="S54" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>540</v>
@@ -7801,457 +7804,468 @@
       <c r="I55" s="1" t="s">
         <v>541</v>
       </c>
+      <c r="J55"/>
       <c r="K55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S55" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="J56"/>
+      <c r="K56" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="J57"/>
+      <c r="K57" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S57" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D58" s="1" t="s">
+      <c r="J58"/>
+      <c r="K58" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="O58" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="S58" t="s">
         <v>565</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>572</v>
       </c>
+      <c r="I59" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="J59"/>
       <c r="K59" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="S59" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="255" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>583</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="J60"/>
       <c r="K60" s="1" t="s">
-        <v>584</v>
+        <v>438</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>587</v>
+        <v>367</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="255" x14ac:dyDescent="0.2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>598</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="J61"/>
       <c r="K61" s="1" t="s">
-        <v>448</v>
+        <v>602</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>611</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="J62"/>
       <c r="K62" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
+      </c>
+      <c r="L62" t="s">
+        <v>615</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>282</v>
+        <v>26</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>623</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="J63"/>
       <c r="K63" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="L63" t="s">
+        <v>614</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>625</v>
       </c>
       <c r="O63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="356" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J64"/>
+      <c r="K64" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P64" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P63" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>626</v>
+      <c r="Q64" s="1" t="s">
+        <v>636</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="356" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>643</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="J65"/>
       <c r="K65" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>644</v>
+        <v>279</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>645</v>
+        <v>279</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>646</v>
+        <v>61</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>647</v>
@@ -8282,23 +8296,24 @@
       <c r="I66" s="1" t="s">
         <v>655</v>
       </c>
+      <c r="J66"/>
       <c r="K66" s="1" t="s">
         <v>656</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P66" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P66" s="1" t="s">
+      <c r="Q66" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>657</v>
@@ -8329,123 +8344,126 @@
       <c r="I67" s="1" t="s">
         <v>665</v>
       </c>
+      <c r="J67"/>
       <c r="K67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S67" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="H68" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="J68"/>
+      <c r="K68" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="H68" s="1" t="s">
+    </row>
+    <row r="69" spans="1:19" ht="187" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S68" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="J69"/>
+      <c r="K69" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="I69" s="1" t="s">
+      <c r="L69" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="M69" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="O69" s="1" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="187" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>684</v>
       </c>
@@ -8458,11 +8476,14 @@
       <c r="D70" s="1" t="s">
         <v>686</v>
       </c>
+      <c r="E70" s="1" t="s">
+        <v>687</v>
+      </c>
       <c r="F70" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>689</v>
@@ -8470,272 +8491,274 @@
       <c r="I70" s="1" t="s">
         <v>690</v>
       </c>
+      <c r="J70" t="s">
+        <v>691</v>
+      </c>
       <c r="K70" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>694</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>146</v>
+        <v>367</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>147</v>
+        <v>367</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>113</v>
+        <v>695</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>696</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="N71" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q71" s="1" t="s">
+      <c r="J71"/>
+      <c r="K71" t="s">
         <v>705</v>
       </c>
-      <c r="R71" s="1" t="s">
+      <c r="O71" t="s">
         <v>706</v>
       </c>
+      <c r="P71" t="s">
+        <v>707</v>
+      </c>
       <c r="S71" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="K72" t="s">
         <v>715</v>
       </c>
-      <c r="O72" t="s">
+      <c r="J72"/>
+      <c r="K72" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="P72" t="s">
+      <c r="L72" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="M72" s="1" t="s">
         <v>717</v>
       </c>
+      <c r="O72" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>719</v>
+      </c>
       <c r="S72" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>723</v>
+        <v>893</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>725</v>
-      </c>
+        <v>726</v>
+      </c>
+      <c r="J73"/>
       <c r="K73" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>727</v>
       </c>
       <c r="O73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q73" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="P73" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q73" s="1" t="s">
+      <c r="S73" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="340" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="S73" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="H74" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="J74"/>
+      <c r="K74" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="H74" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="O74" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="P74" t="s">
         <v>737</v>
       </c>
-      <c r="K74" t="s">
-        <v>732</v>
-      </c>
-      <c r="L74" s="1" t="s">
+      <c r="Q74" t="s">
+        <v>737</v>
+      </c>
+      <c r="S74" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="O74" t="s">
-        <v>732</v>
-      </c>
-      <c r="P74" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q74" s="1" t="s">
+    </row>
+    <row r="75" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="S74" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" ht="340" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="F75" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>744</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>745</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>745</v>
       </c>
+      <c r="J75"/>
       <c r="K75" s="1" t="s">
         <v>746</v>
       </c>
       <c r="L75" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="M75" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="O75" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="P75" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q75" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="O75" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P75" t="s">
+      <c r="S75" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="Q75" t="s">
-        <v>749</v>
-      </c>
-      <c r="S75" s="1" t="s">
+    </row>
+    <row r="76" spans="1:19" ht="272" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>752</v>
@@ -8755,6 +8778,7 @@
       <c r="I76" s="1" t="s">
         <v>757</v>
       </c>
+      <c r="J76"/>
       <c r="K76" s="1" t="s">
         <v>758</v>
       </c>
@@ -8765,113 +8789,126 @@
         <v>759</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P76" t="s">
-        <v>749</v>
+        <v>26</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="Q76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S76" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="S76" s="1" t="s">
+    </row>
+    <row r="77" spans="1:19" ht="204" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" ht="272" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="H77" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="I77" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="J77"/>
+      <c r="K77" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="L77" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S77" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="I77" s="1" t="s">
+    </row>
+    <row r="78" spans="1:19" ht="388" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="O77" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="J78" t="s">
+        <v>777</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P78" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P77" s="1" t="s">
+      <c r="Q78" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q77" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="204" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="K78" s="1" t="s">
+      <c r="R78" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" ht="388" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>781</v>
       </c>
@@ -8894,383 +8931,335 @@
         <v>786</v>
       </c>
       <c r="H79" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="J79" t="s">
         <v>788</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="K79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="S79" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="K79" s="1" t="s">
+    </row>
+    <row r="80" spans="1:19" ht="388" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="J80" t="s">
+        <v>797</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="P80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="S80" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="404" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="J81" t="s">
+        <v>807</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O81" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="P81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="S81" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="388" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="J82" t="s">
+        <v>817</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N79" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="O79" s="1" t="s">
+      <c r="P82" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P79" s="1" t="s">
+      <c r="Q82" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q79" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R79" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="S79" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P80" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P81" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="I82" s="1" t="s">
+      <c r="R82" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="S82" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P82" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q82" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="J83"/>
+      <c r="K83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q83" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="S83" s="1" t="s">
         <v>826</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="P83" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q83" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R83" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="D84" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="J84" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="I84" s="1" t="s">
+      <c r="K84" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="L84" s="1" t="s">
-        <v>71</v>
+        <v>895</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>346</v>
+        <v>366</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>896</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>429</v>
+        <v>124</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q84" s="1" t="s">
         <v>838</v>
       </c>
+      <c r="Q84" t="s">
+        <v>839</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>897</v>
+      </c>
       <c r="S84" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="P85" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>854</v>
-      </c>
-      <c r="R85" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="S85" s="1" t="s">
-        <v>856</v>
-      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9286,7 +9275,7 @@
     <col min="3" max="3" width="20.6640625" customWidth="1"/>
     <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -9294,1516 +9283,1675 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="F1" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="F1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>867</v>
+        <v>850</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>868</v>
+        <v>851</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="323" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="289" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>864</v>
+        <v>847</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="174" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="202" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>865</v>
+        <v>848</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="227" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="223" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="306" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C20" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="D22" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>873</v>
+        <v>856</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="289" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="272" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>874</v>
+        <v>857</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="E42" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>514</v>
+        <v>503</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="153" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="170" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="197" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="C57" s="1" t="s">
+      <c r="D58" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="221" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="197" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="B59" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B59" t="s">
-        <v>592</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>895</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="B60" t="s">
+        <v>582</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B61" t="s">
+        <v>596</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="170" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="B61" s="1" t="s">
+    </row>
+    <row r="62" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="187" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="B63" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C62" s="1" t="s">
+      <c r="B64" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>897</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="B63" s="1" t="s">
+      <c r="D64" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="340" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="B65" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="340" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B64" s="1" t="s">
+    <row r="66" spans="1:6" ht="306" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>657</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="306" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="136" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>683</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="312" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A71" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="B72" t="s">
+        <v>710</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="E72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B73" t="s">
+        <v>710</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
-        <v>708</v>
-      </c>
-      <c r="B71" t="s">
-        <v>720</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="F73" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="187" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B75" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="F74" s="1" t="s">
+      <c r="B76" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="170" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="B77" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="C78" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+    <row r="79" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>793</v>
+      <c r="D79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="136" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>831</v>
+      <c r="C83" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>840</v>
       </c>
     </row>
